--- a/docs/教程.xlsx
+++ b/docs/教程.xlsx
@@ -27,7 +27,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04-跨语言取值'!$A$1:$G$223</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05-文案规范'!$A$1:$C$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06-验收清单'!$A$1:$C$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'07-踩坑'!$A$1:$C$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'07-踩坑'!$A$1:$C$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'08-文案样例'!$A$1:$E$121</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'09-枚举速查'!$A$1:$G$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'10-站点专属取值'!$A$1:$D$26</definedName>
@@ -16953,7 +16953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -16981,226 +16981,294 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>枚举查不到</t>
+          <t>copy 被 vocab 劫持</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>definedName 生成时把 `[ ] # =` 删掉了，拼键时也要删；否则 2674 个名字一个都匹配不上。</t>
+          <t>vocab 是从历史表反推的，里面也有 contribution_sku / model_number / product_id_value（值是 SKU/ASIN），映射先于 copy 走就会报「值映射缺项」并整份不写。</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>flatfile.AllowedValues.get() 统一处理</t>
+          <t>fill.py 顺序固定 text → copy → vocab/value_map</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>openpyxl 保存毁文件</t>
+          <t>父体行不算必填</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>openpyxl 保存 xlsm 会丢 xl/media 里的图片、把 sharedStrings 改成内联字符串、动 drawing 引用。</t>
+          <t>size/颜色/价格/配送/parent_sku 只有子体行才有；按全表计必填会天天刷假 FAIL。</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>改用 zip + XML 手术，只替换 1 个 sheet part 和 sharedStrings</t>
+          <t>check.py 用 VARIANT_ONLY + parent_rows 只算子体行</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>WPS 二次保存</t>
+          <t>条件必填被当硬必填</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>用户在 WPS 里打开再存：条目 44→55，13 张图被重编码改名，还加 docProps/custom.xml。</t>
+          <t>ES 模板写 Obligatorio condicionalmente，startswith('obligatorio') 会误判，一次刷 70+ 条假 FAIL。</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>交付后不要让 WPS 保存；发现条目数变了就重跑 fill.py</t>
+          <t>先判条件必填再判硬必填，状态词表见 SKILL.md</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>文件被占用</t>
+          <t>模板被预筛过</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>目标文件开着时 os.replace 报 WinError 5 / PermissionError。</t>
+          <t>在后台按单个 ASIN 下载的模板，browse node 下拉只剩该商品一个节点（荷兰那份只剩 Bikini's &gt; Sets），拿去上 Tankini/连体款就是错类目。</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>先查 `~$文件名` 锁文件与 EXCEL/WPS 进程，关闭后再写</t>
+          <t>enums.py --attr recommended_browse_nodes 看节点数，≤5 就重新下通用模板</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>父体行不能有变体值</t>
+          <t>枚举查不到</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>父体填 size/color、或子体缺 parent_sku，都会报变体关系错误。</t>
+          <t>definedName 生成时把 `[ ] # =` 删掉了，拼键时也要删；否则 2674 个名字一个都匹配不上。</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>fill.py 按源表空值跳过，check.py 有专门校验</t>
+          <t>flatfile.AllowedValues.get() 统一处理</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>价格被写成文本</t>
+          <t>openpyxl 保存毁文件</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>源表价格是文本 '39.99'，直接搬会变成字符串，影响价格解析。</t>
+          <t>openpyxl 保存 xlsm 会丢 xl/media 里的图片、把 sharedStrings 改成内联字符串、动 drawing 引用。</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>配置 numeric 列表强制转 float</t>
+          <t>改用 zip + XML 手术，只替换 1 个 sheet part 和 sharedStrings</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GTIN 豁免</t>
+          <t>WPS 二次保存</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>父体常写 GTIN-vrijgesteld / GTIN Exempt / GTIN-Freistellung，前提是品牌已获批豁免。</t>
+          <t>用户在 WPS 里打开再存：条目 44→55，13 张图被重编码改名，还加 docProps/custom.xml。</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>与源站点保持一致，不要自造 GTIN</t>
+          <t>交付后不要让 WPS 保存；发现条目数变了就重跑 fill.py</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>浏览节点每站不同</t>
+          <t>文件被占用</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>同一个商品各站 browse node 名称与 ID 都不一样，不能照抄。</t>
+          <t>目标文件开着时 os.replace 报 WinError 5 / PermissionError。</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>用 enums.py 取目标站 recommended_browse_nodes 的唯一合法值</t>
+          <t>先查 `~$文件名` 锁文件与 EXCEL/WPS 进程，关闭后再写</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>西班牙站标签不规范</t>
+          <t>父体行不能有变体值</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>ES 模板 parentage 取值是 'Principal.' 和 'Niños'（带句号/复数），不要按语义硬翻。</t>
+          <t>父体填 size/color、或子体缺 parent_sku，都会报变体关系错误。</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>以 04 页签的实测对照为准</t>
+          <t>fill.py 按源表空值跳过，check.py 有专门校验</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>后台关键词重复标题</t>
+          <t>价格被写成文本</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>把标题词再塞进后端，浪费索引位。</t>
+          <t>源表价格是文本 '39.99'，直接搬会变成字符串，影响价格解析。</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>只放同义词/场景词，check.py 会 WARN</t>
+          <t>配置 numeric 列表强制转 float</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>五点多写一个</t>
+          <t>GTIN 豁免</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>荷兰/德国站模板只有 5 个 bullet_point 列，第 6 个写不进去。</t>
+          <t>父体常写 GTIN-vrijgesteld / GTIN Exempt / GTIN-Freistellung，前提是品牌已获批豁免。</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>严格 5 条</t>
+          <t>与源站点保持一致，不要自造 GTIN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>合规字段别自造</t>
+          <t>浏览节点每站不同</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>compliance_has_lining / compliance_has_inner_brief 等是 EU 新增合规声明，属实质申报。</t>
+          <t>同一个商品各站 browse node 名称与 ID 都不一样，不能照抄。</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>源站点没写的，目标站点也不写，让客户确认</t>
+          <t>用 enums.py 取目标站 recommended_browse_nodes 的唯一合法值</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>西班牙站标签不规范</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>ES 模板 parentage 取值是 'Principal.' 和 'Niños'（带句号/复数），不要按语义硬翻。</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>以 04 页签的实测对照为准</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>后台关键词重复标题</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>把标题词再塞进后端，浪费索引位。</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>只放同义词/场景词，check.py 会 WARN</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>五点多写一个</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>荷兰/德国站模板只有 5 个 bullet_point 列，第 6 个写不进去。</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>严格 5 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>合规字段别自造</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>compliance_has_lining / compliance_has_inner_brief 等是 EU 新增合规声明，属实质申报。</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>源站点没写的，目标站点也不写，让客户确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>尺码写法差异</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>FR 的 M/L/XL 是 Moyen / Grand (l) / TG / TTG (xx_l)，不是 M/L/XL。</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>用 04 页签对照，别用字母原文</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C14"/>
+  <autoFilter ref="A1:C18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/教程.xlsx
+++ b/docs/教程.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>① 枚举值只填目标站 official dropdown 里的值；② 源站点没写的字段，目标站点也不写（尤其合规声明）；③ 父体行不填 size/颜色，子体行必须填 parent_sku。</t>
+          <t>① 枚举值只填目标站 official dropdown 里的值；② 源站点没写的字段，目标站点也不写（尤其合规声明）；③ 父体行不填 size/颜色，子体行必须填 parent_sku；④ 产出统一命名 &lt;国家&gt;-&lt;sku&gt;-上传表-dsh生成.xlsm，dsh生成 必带。</t>
         </is>
       </c>
     </row>

--- a/docs/教程.xlsx
+++ b/docs/教程.xlsx
@@ -21,13 +21,13 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'00-速查'!$A$1:$B$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01-流程'!$A$1:$E$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01-流程'!$A$1:$E$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02-站点对照'!$A$1:$F$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03-属性处理'!$A$1:$E$224</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04-跨语言取值'!$A$1:$G$223</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05-文案规范'!$A$1:$C$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06-验收清单'!$A$1:$C$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'07-踩坑'!$A$1:$C$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'07-踩坑'!$A$1:$C$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'08-文案样例'!$A$1:$E$121</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'09-枚举速查'!$A$1:$G$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'10-站点专属取值'!$A$1:$D$26</definedName>
@@ -3059,7 +3059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3098,256 +3098,281 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>摸结构</t>
+          <t>选模板</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>probe.py 看两表的 marketplace_id / language_tag / 属性数 / 数据行 / 已填属性</t>
+          <t>pick_template.py 按类目词（bikini/tankini/monokini）自动挑目标站空白模板；节点数≤5 说明是按单个 ASIN 预筛的，只能干那一个类目</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>两张表的属性名清单</t>
+          <t>目标模板路径</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>两表数据行数一致；确认第 5 行是属性名、第 7 行起是数据</t>
+          <t>推荐模板覆盖源表类目，且没有数据行</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>对列</t>
+          <t>摸结构</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>按 normalize 后的属性名（删 marketplace_id、language_tag、[]#=）自动建 DE列→目标列 映射</t>
+          <t>probe.py 看两表的 marketplace_id / language_tag / 属性数 / 数据行 / 已填属性</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>映射表（脚本自动生成，不手抄列号）</t>
+          <t>两张表的属性名清单</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>源表有值、目标表没这列的要列出来单独判断（例：item_shape 荷兰模板没有）</t>
+          <t>两表数据行数一致；确认第 5 行是属性名、第 7 行起是数据</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>查枚举</t>
+          <t>对列</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>从 workbook.xml 的 definedNames 找到 SWIMWEAR+属性 指向 Dropdown Lists 的区间，读出官方允许值</t>
+          <t>按 normalize 后的属性名（删 marketplace_id、language_tag、[]#=）自动建 DE列→目标列 映射</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>每字段合法取值集合</t>
+          <t>映射表（脚本自动生成，不手抄列号）</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>脚本必须把 `[ ] # =` 全删掉再拼名字，否则查不到</t>
+          <t>源表有值、目标表没这列的要列出来单独判断（例：item_shape 荷兰模板没有）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>翻译取值</t>
+          <t>查枚举</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>优先用 vocab_de_eu.tsv（历史成交文件反推的实测对照）；vocab 里没有的，人工按官方列表挑，并在配置里写 value_map</t>
+          <t>从 workbook.xml 的 definedNames 找到 SWIMWEAR+属性 指向 Dropdown Lists 的区间，读出官方允许值</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>value_map / vocab</t>
+          <t>每字段合法取值集合</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>查不到就报错停下，绝不猜一个相近的值</t>
+          <t>脚本必须把 `[ ] # =` 全删掉再拼名字，否则查不到</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>写文案</t>
+          <t>翻译取值</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>标题≤75、副标题≤125、五点各≤500（第2条≤700）、描述≤2000、关键词≤250；文案结构沿用源站点五段式</t>
+          <t>优先用 vocab_de_eu.tsv（历史成交文件反推的实测对照）；vocab 里没有的，人工按官方列表挑，并在配置里写 value_map</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>text 段</t>
+          <t>value_map / vocab</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>主标题品牌开头、无促销词、无全角标点、关键词不重复标题词</t>
+          <t>查不到就报错停下，绝不猜一个相近的值</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>搬硬字段</t>
+          <t>写文案</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>SKU / parent_sku / brand / product_id / model / price / dims / weight / fulfillment 原样搬（copy+numeric）</t>
+          <t>标题≤75、副标题≤125、五点各≤500（第2条≤700）、描述≤2000、关键词≤250；文案结构沿用源站点五段式</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>copy、numeric 段</t>
+          <t>text 段</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>价格按数字写；父体行不要有 price/size</t>
+          <t>主标题品牌开头、无促销词、无全角标点、关键词不重复标题词</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>写入</t>
+          <t>搬硬字段</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>fill.py 走 XML 手术：替换目标 sheet part + sharedStrings，dimension 扩到末行，其余条目按原 date_time/external_attr 回写</t>
+          <t>SKU / parent_sku / brand / product_id / model / price / dims / weight / fulfillment 原样搬（copy+numeric）</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>新 xlsm（与原表同目录，原表不动）</t>
+          <t>copy、numeric 段</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>zip 条目数与空白模板一致（44/44）</t>
+          <t>价格按数字写；父体行不要有 price/size</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>复读校验</t>
+          <t>写入</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>openpyxl 重新打开：表头 1–6 行与空白模板差异必须为 0；源→目标逐格对照缺 0 格多 0 格</t>
+          <t>fill.py 走 XML 手术：替换目标 sheet part + sharedStrings，dimension 扩到末行，其余条目按原 date_time/external_attr 回写</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>校验输出</t>
+          <t>新 xlsm（与原表同目录，原表不动）</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>差异 0 才继续</t>
+          <t>zip 条目数与空白模板一致（44/44）</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>体检</t>
+          <t>复读校验</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>check.py：zip/XML/表头/必填/枚举/文案/变体/价格关系</t>
+          <t>openpyxl 重新打开：表头 1–6 行与空白模板差异必须为 0；源→目标逐格对照缺 0 格多 0 格</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>体检报告</t>
+          <t>校验输出</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>FAIL=0；WARN 逐条判断（条件必填多为此类目不适用）</t>
+          <t>差异 0 才继续</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>体检</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>check.py：zip/XML/表头/必填/枚举/文案/变体/价格关系</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>体检报告</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>FAIL=0；WARN 逐条判断（条件必填多为此类目不适用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>交付</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>产出命名 `&lt;目标表名&gt;_&lt;语言&gt;填写_德国&lt;编号&gt;.xlsm`，与目标表同目录；不要用 WPS 二次保存</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>可上传文件</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>WPS 另存会重排图片部件，文件结构与模板不再一致</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E11"/>
+  <autoFilter ref="A1:E12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16953,7 +16978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -17049,226 +17074,243 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>枚举查不到</t>
+          <t>下拉里没有对应值</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>definedName 生成时把 `[ ] # =` 删掉了，拼键时也要删；否则 2674 个名字一个都匹配不上。</t>
+          <t>目标站允许列表里找不到源值；或配置压根没覆盖这个受控字段。</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>flatfile.AllowedValues.get() 统一处理</t>
+          <t>留空 + 写 &lt;产出&gt;.pending.tsv 清单问客户；fill.py --strict 才中断。优先级：模板已有值 &gt; 允许列表近义值 &gt; 留空问</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>openpyxl 保存毁文件</t>
+          <t>枚举查不到</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>openpyxl 保存 xlsm 会丢 xl/media 里的图片、把 sharedStrings 改成内联字符串、动 drawing 引用。</t>
+          <t>definedName 生成时把 `[ ] # =` 删掉了，拼键时也要删；否则 2674 个名字一个都匹配不上。</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>改用 zip + XML 手术，只替换 1 个 sheet part 和 sharedStrings</t>
+          <t>flatfile.AllowedValues.get() 统一处理</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>WPS 二次保存</t>
+          <t>openpyxl 保存毁文件</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>用户在 WPS 里打开再存：条目 44→55，13 张图被重编码改名，还加 docProps/custom.xml。</t>
+          <t>openpyxl 保存 xlsm 会丢 xl/media 里的图片、把 sharedStrings 改成内联字符串、动 drawing 引用。</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>交付后不要让 WPS 保存；发现条目数变了就重跑 fill.py</t>
+          <t>改用 zip + XML 手术，只替换 1 个 sheet part 和 sharedStrings</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>文件被占用</t>
+          <t>WPS 二次保存</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>目标文件开着时 os.replace 报 WinError 5 / PermissionError。</t>
+          <t>用户在 WPS 里打开再存：条目 44→55，13 张图被重编码改名，还加 docProps/custom.xml。</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>先查 `~$文件名` 锁文件与 EXCEL/WPS 进程，关闭后再写</t>
+          <t>交付后不要让 WPS 保存；发现条目数变了就重跑 fill.py</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>父体行不能有变体值</t>
+          <t>文件被占用</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>父体填 size/color、或子体缺 parent_sku，都会报变体关系错误。</t>
+          <t>目标文件开着时 os.replace 报 WinError 5 / PermissionError。</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>fill.py 按源表空值跳过，check.py 有专门校验</t>
+          <t>先查 `~$文件名` 锁文件与 EXCEL/WPS 进程，关闭后再写</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>价格被写成文本</t>
+          <t>父体行不能有变体值</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>源表价格是文本 '39.99'，直接搬会变成字符串，影响价格解析。</t>
+          <t>父体填 size/color、或子体缺 parent_sku，都会报变体关系错误。</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>配置 numeric 列表强制转 float</t>
+          <t>fill.py 按源表空值跳过，check.py 有专门校验</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GTIN 豁免</t>
+          <t>价格被写成文本</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>父体常写 GTIN-vrijgesteld / GTIN Exempt / GTIN-Freistellung，前提是品牌已获批豁免。</t>
+          <t>源表价格是文本 '39.99'，直接搬会变成字符串，影响价格解析。</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>与源站点保持一致，不要自造 GTIN</t>
+          <t>配置 numeric 列表强制转 float</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浏览节点每站不同</t>
+          <t>GTIN 豁免</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>同一个商品各站 browse node 名称与 ID 都不一样，不能照抄。</t>
+          <t>父体常写 GTIN-vrijgesteld / GTIN Exempt / GTIN-Freistellung，前提是品牌已获批豁免。</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>用 enums.py 取目标站 recommended_browse_nodes 的唯一合法值</t>
+          <t>与源站点保持一致，不要自造 GTIN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>西班牙站标签不规范</t>
+          <t>浏览节点每站不同</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>ES 模板 parentage 取值是 'Principal.' 和 'Niños'（带句号/复数），不要按语义硬翻。</t>
+          <t>同一个商品各站 browse node 名称与 ID 都不一样，不能照抄。</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>以 04 页签的实测对照为准</t>
+          <t>用 enums.py 取目标站 recommended_browse_nodes 的唯一合法值</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>后台关键词重复标题</t>
+          <t>西班牙站标签不规范</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>把标题词再塞进后端，浪费索引位。</t>
+          <t>ES 模板 parentage 取值是 'Principal.' 和 'Niños'（带句号/复数），不要按语义硬翻。</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>只放同义词/场景词，check.py 会 WARN</t>
+          <t>以 04 页签的实测对照为准</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>五点多写一个</t>
+          <t>后台关键词重复标题</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>荷兰/德国站模板只有 5 个 bullet_point 列，第 6 个写不进去。</t>
+          <t>把标题词再塞进后端，浪费索引位。</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>严格 5 条</t>
+          <t>只放同义词/场景词，check.py 会 WARN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>合规字段别自造</t>
+          <t>五点多写一个</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>compliance_has_lining / compliance_has_inner_brief 等是 EU 新增合规声明，属实质申报。</t>
+          <t>荷兰/德国站模板只有 5 个 bullet_point 列，第 6 个写不进去。</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>源站点没写的，目标站点也不写，让客户确认</t>
+          <t>严格 5 条</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>合规字段别自造</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>compliance_has_lining / compliance_has_inner_brief 等是 EU 新增合规声明，属实质申报。</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>源站点没写的，目标站点也不写，让客户确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
           <t>尺码写法差异</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>FR 的 M/L/XL 是 Moyen / Grand (l) / TG / TTG (xx_l)，不是 M/L/XL。</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>用 04 页签对照，别用字母原文</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C18"/>
+  <autoFilter ref="A1:C19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/教程.xlsx
+++ b/docs/教程.xlsx
@@ -18,6 +18,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08-文案样例" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09-枚举速查" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10-站点专属取值" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11-模板清单" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'00-速查'!$A$1:$B$16</definedName>
@@ -31,6 +32,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'08-文案样例'!$A$1:$E$121</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'09-枚举速查'!$A$1:$G$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'10-站点专属取值'!$A$1:$D$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'11-模板清单'!$A$1:$F$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3053,6 +3055,381 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>国家</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>模板文件</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>browse node 数</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>性质</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>覆盖类目</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>有数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>德国</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>德国空白上传模版.xlsx</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>全量</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>bikini/monokini/tankini</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>德国</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>惠全优 德国 2399.xlsm</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>预筛(单类目)</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>bikini</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>比利时</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>比利时空白上传表.xlsm</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>全量</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>bikini/monokini/onepiece/tankini</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>法国</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>法国空白上传模版.xlsm</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>全量</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>bikini/monokini/onepiece/tankini</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>英国</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>1391.xlsm</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>全量</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>bikini/monokini/onepiece/tankini</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>英国</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>英国空白上传模版.xlsm</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>全量</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>bikini/monokini/onepiece/tankini</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>荷兰</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>takini set 模板.xlsm</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>预筛(单类目)</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>tankini</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>荷兰</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>荷兰 monokini空白模版.xlsm</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>全量</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>bikini/monokini/onepiece/tankini</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>荷兰</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>荷兰空白上传模版.xlsm</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>预筛(单类目)</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>bikini</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>西班牙</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>西班牙空白上传模版.xlsm</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>全量</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>bikini/monokini/onepiece/tankini</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F11"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
